--- a/master-db/kgm.xlsx
+++ b/master-db/kgm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kang1\Documents\GitHub\ildeung-battery-v1\master-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA6937C6-BE5D-4C5F-AEF1-7FBEAE7DFDD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9801C83-2B70-4C72-93AE-B2B4B74027A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="125">
   <si>
     <t>제조사</t>
   </si>
@@ -59,9 +59,6 @@
     <t>가솔린</t>
   </si>
   <si>
-    <t>렉스턴 (01/09~03/12) 가솔린</t>
-  </si>
-  <si>
     <t>DF80R</t>
   </si>
   <si>
@@ -71,63 +68,33 @@
     <t>디젤</t>
   </si>
   <si>
-    <t>렉스턴 (01/09~03/12) 디젤</t>
-  </si>
-  <si>
     <t>DF90R</t>
   </si>
   <si>
     <t>03/12~06/03</t>
   </si>
   <si>
-    <t>뉴렉스턴 (03/12~06/03) 가솔린</t>
-  </si>
-  <si>
-    <t>뉴렉스턴 (03/12~06/03) 디젤</t>
-  </si>
-  <si>
     <t>06/03~08~07</t>
   </si>
   <si>
-    <t>렉스턴2 (06/03~08~07) 디젤</t>
-  </si>
-  <si>
     <t>08/07~12/06</t>
   </si>
   <si>
-    <t>슈퍼렉스턴 (08/07~12/06) 디젤</t>
-  </si>
-  <si>
     <t>12/06~17/05</t>
   </si>
   <si>
-    <t>렉스턴W (12/06~17/05) 디젤</t>
-  </si>
-  <si>
     <t>17/05~20/11</t>
   </si>
   <si>
-    <t>G4렉스턴 (17/05~20/11) 디젤</t>
-  </si>
-  <si>
     <t>18년~</t>
   </si>
   <si>
-    <t>렉스턴스포츠 (18년~) 디젤</t>
-  </si>
-  <si>
     <t>19년~</t>
   </si>
   <si>
-    <t>렉스턴스포츠 칸 (19년~) 디젤</t>
-  </si>
-  <si>
     <t>2020/11~</t>
   </si>
   <si>
-    <t>올뉴렉스턴 (2020/11~) 디젤</t>
-  </si>
-  <si>
     <t>AGM80</t>
   </si>
   <si>
@@ -137,117 +104,66 @@
     <t>04~07년</t>
   </si>
   <si>
-    <t>로디우스 (04~07년) 디젤</t>
-  </si>
-  <si>
     <t>07~12년</t>
   </si>
   <si>
-    <t>뉴로디우스 (07~12년)</t>
-  </si>
-  <si>
     <t>12~13년</t>
   </si>
   <si>
-    <t>로디우스 유로 (12~13년)</t>
-  </si>
-  <si>
     <t>무쏘</t>
   </si>
   <si>
     <t>2000년07월이전</t>
   </si>
   <si>
-    <t>무쏘 (2000년07월이전) 디젤</t>
-  </si>
-  <si>
     <t>DF90L</t>
   </si>
   <si>
-    <t>무쏘 (2000년07월이전) 가솔린</t>
-  </si>
-  <si>
     <t>DF80L</t>
   </si>
   <si>
     <t>2000년07월이후</t>
   </si>
   <si>
-    <t>무쏘 (2000년07월이후) 디젤</t>
-  </si>
-  <si>
-    <t>무쏘 (2000년07월이후) 가솔린</t>
-  </si>
-  <si>
     <t>액티언</t>
   </si>
   <si>
     <t>05~11년</t>
   </si>
   <si>
-    <t>액티언 (05~11년) 디젤</t>
-  </si>
-  <si>
     <t>06~11년</t>
   </si>
   <si>
-    <t>액티언 스포츠 (06~11년) 디젤</t>
-  </si>
-  <si>
     <t>체어맨</t>
   </si>
   <si>
     <t>97~03년</t>
   </si>
   <si>
-    <t>체어맨 (97~03년)</t>
-  </si>
-  <si>
     <t>DIN100L</t>
   </si>
   <si>
     <t>03~08년</t>
   </si>
   <si>
-    <t>뉴체어맨 (03~08년)</t>
-  </si>
-  <si>
     <t>08~11년</t>
   </si>
   <si>
-    <t>체어맨W (08~11년)</t>
-  </si>
-  <si>
     <t>11~17년</t>
   </si>
   <si>
-    <t>뉴체어맨W (11~17년)</t>
-  </si>
-  <si>
-    <t>체어맨H (08~11년)</t>
-  </si>
-  <si>
     <t>11~14년</t>
   </si>
   <si>
-    <t>체어맨H뉴클래식 (11~14년)</t>
-  </si>
-  <si>
     <t>카이런</t>
   </si>
   <si>
     <t>05~07년</t>
   </si>
   <si>
-    <t>카이런 (05~07년) 디젤</t>
-  </si>
-  <si>
     <t>07~11년</t>
   </si>
   <si>
-    <t>뉴카이런 (07~11년) 디젤</t>
-  </si>
-  <si>
     <t>코란도</t>
   </si>
   <si>
@@ -257,33 +173,18 @@
     <t>69~96년</t>
   </si>
   <si>
-    <t>코란도 (69~96년) 디젤</t>
-  </si>
-  <si>
     <t>88~96년</t>
   </si>
   <si>
-    <t>코란도훼밀리 (88~96년)</t>
-  </si>
-  <si>
     <t>96~05년</t>
   </si>
   <si>
-    <t>뉴코란도 (96~05년)</t>
-  </si>
-  <si>
     <t>11~13년</t>
   </si>
   <si>
-    <t>코란도C (11~13년)</t>
-  </si>
-  <si>
     <t>12~16년</t>
   </si>
   <si>
-    <t>코란도스포츠 (12~16년)</t>
-  </si>
-  <si>
     <t>13년~</t>
   </si>
   <si>
@@ -413,6 +314,592 @@
   </si>
   <si>
     <t>DIN60HL</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>렉스턴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뉴렉스턴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>렉스턴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">2 </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>슈퍼렉스턴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>렉스턴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">W </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>G4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>렉스턴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>렉스턴스포츠</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>올뉴렉스턴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>로디우스</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뉴로디우스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>로디우스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>유로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>무쏘</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>무쏘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>액티언</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>액티언</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스포츠</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>체어맨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뉴체어맨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>체어맨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">W </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뉴체어맨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">W </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>체어맨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">H </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>체어맨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뉴클래식</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>카이런</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뉴카이런</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>코란도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>코란도훼밀리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뉴코란도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>코란도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">C </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>코란도스포츠</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -420,7 +907,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -443,6 +930,20 @@
     <font>
       <sz val="8"/>
       <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF111827"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF111827"/>
+      <name val="Carlito"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
@@ -473,7 +974,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -486,6 +987,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -743,15 +1250,15 @@
       <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="21" customHeight="1">
@@ -765,17 +1272,17 @@
         <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="21" customHeight="1">
@@ -786,20 +1293,20 @@
         <v>9</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>19</v>
+      <c r="E4" s="5" t="s">
+        <v>98</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="21" customHeight="1">
@@ -810,20 +1317,20 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="21" customHeight="1">
@@ -834,20 +1341,20 @@
         <v>9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="21" customHeight="1">
@@ -858,20 +1365,20 @@
         <v>9</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="21" customHeight="1">
@@ -882,20 +1389,20 @@
         <v>9</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="21" customHeight="1">
@@ -906,20 +1413,20 @@
         <v>9</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="21" customHeight="1">
@@ -930,20 +1437,20 @@
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="21" customHeight="1">
@@ -954,20 +1461,20 @@
         <v>9</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="21" customHeight="1">
@@ -978,20 +1485,20 @@
         <v>9</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>34</v>
+        <v>14</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="21" customHeight="1">
@@ -999,23 +1506,23 @@
         <v>8</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="21" customHeight="1">
@@ -1023,21 +1530,21 @@
         <v>8</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D14" s="2"/>
-      <c r="E14" s="2" t="s">
-        <v>40</v>
+      <c r="E14" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="21" customHeight="1">
@@ -1045,21 +1552,21 @@
         <v>8</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D15" s="2"/>
-      <c r="E15" s="2" t="s">
-        <v>42</v>
+      <c r="E15" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="21" customHeight="1">
@@ -1067,23 +1574,23 @@
         <v>8</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>45</v>
+        <v>14</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>108</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="21" customHeight="1">
@@ -1091,23 +1598,23 @@
         <v>8</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>47</v>
+      <c r="E17" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="21" customHeight="1">
@@ -1115,23 +1622,23 @@
         <v>8</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="21" customHeight="1">
@@ -1139,23 +1646,23 @@
         <v>8</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>51</v>
+      <c r="E19" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="21" customHeight="1">
@@ -1163,23 +1670,23 @@
         <v>8</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="D20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="21" customHeight="1">
@@ -1187,23 +1694,23 @@
         <v>8</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="D21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="21" customHeight="1">
@@ -1211,21 +1718,21 @@
         <v>8</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D22" s="2"/>
-      <c r="E22" s="2" t="s">
-        <v>59</v>
+      <c r="E22" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="21" customHeight="1">
@@ -1233,21 +1740,21 @@
         <v>8</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="D23" s="2"/>
-      <c r="E23" s="2" t="s">
-        <v>62</v>
+      <c r="E23" s="5" t="s">
+        <v>113</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="21" customHeight="1">
@@ -1255,21 +1762,21 @@
         <v>8</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="D24" s="2"/>
-      <c r="E24" s="2" t="s">
-        <v>64</v>
+      <c r="E24" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="21" customHeight="1">
@@ -1277,21 +1784,21 @@
         <v>8</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="D25" s="2"/>
-      <c r="E25" s="2" t="s">
-        <v>66</v>
+      <c r="E25" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="21" customHeight="1">
@@ -1299,21 +1806,21 @@
         <v>8</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="D26" s="2"/>
-      <c r="E26" s="2" t="s">
-        <v>67</v>
+      <c r="E26" s="5" t="s">
+        <v>116</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="21" customHeight="1">
@@ -1321,21 +1828,21 @@
         <v>8</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="D27" s="2"/>
-      <c r="E27" s="2" t="s">
-        <v>69</v>
+      <c r="E27" s="5" t="s">
+        <v>117</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="21" customHeight="1">
@@ -1343,23 +1850,23 @@
         <v>8</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="D28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="21" customHeight="1">
@@ -1367,23 +1874,23 @@
         <v>8</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="D29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="21" customHeight="1">
@@ -1391,21 +1898,21 @@
         <v>8</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="21" customHeight="1">
@@ -1413,23 +1920,23 @@
         <v>8</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="D31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F31" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="G31" s="2"/>
       <c r="H31" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="21" customHeight="1">
@@ -1437,21 +1944,21 @@
         <v>8</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="D32" s="2"/>
-      <c r="E32" s="2" t="s">
-        <v>80</v>
+      <c r="E32" s="5" t="s">
+        <v>121</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="21" customHeight="1">
@@ -1459,21 +1966,21 @@
         <v>8</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="D33" s="2"/>
-      <c r="E33" s="2" t="s">
-        <v>82</v>
+      <c r="E33" s="5" t="s">
+        <v>122</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="21" customHeight="1">
@@ -1481,21 +1988,21 @@
         <v>8</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="D34" s="2"/>
-      <c r="E34" s="2" t="s">
-        <v>84</v>
+      <c r="E34" s="5" t="s">
+        <v>123</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="21" customHeight="1">
@@ -1503,21 +2010,21 @@
         <v>8</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="D35" s="2"/>
-      <c r="E35" s="2" t="s">
-        <v>86</v>
+      <c r="E35" s="5" t="s">
+        <v>124</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G35" s="2"/>
       <c r="H35" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="21" customHeight="1">
@@ -1525,21 +2032,21 @@
         <v>8</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G36" s="2"/>
       <c r="H36" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="21" customHeight="1">
@@ -1547,21 +2054,21 @@
         <v>8</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2" t="s">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G37" s="2"/>
       <c r="H37" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="21" customHeight="1">
@@ -1569,21 +2076,21 @@
         <v>8</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G38" s="2"/>
       <c r="H38" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="21" customHeight="1">
@@ -1591,21 +2098,21 @@
         <v>8</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2" t="s">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G39" s="2"/>
       <c r="H39" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="21" customHeight="1">
@@ -1613,23 +2120,23 @@
         <v>8</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="G40" s="2"/>
       <c r="H40" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="21" customHeight="1">
@@ -1637,23 +2144,23 @@
         <v>8</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="G41" s="2"/>
       <c r="H41" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="21" customHeight="1">
@@ -1661,25 +2168,25 @@
         <v>8</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>128</v>
+        <v>95</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="21" customHeight="1">
@@ -1687,23 +2194,23 @@
         <v>8</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="21" customHeight="1">
@@ -1711,25 +2218,25 @@
         <v>8</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>128</v>
+        <v>95</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="21" customHeight="1">
@@ -1737,23 +2244,23 @@
         <v>8</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="G45" s="2"/>
       <c r="H45" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="21" customHeight="1">
@@ -1761,25 +2268,25 @@
         <v>8</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>128</v>
+        <v>95</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="21" customHeight="1">
@@ -1787,23 +2294,23 @@
         <v>8</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="G47" s="2"/>
       <c r="H47" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="21" customHeight="1">
@@ -1811,23 +2318,23 @@
         <v>8</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="G48" s="2"/>
       <c r="H48" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="21" customHeight="1">
@@ -1835,23 +2342,23 @@
         <v>8</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>111</v>
+        <v>78</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="G49" s="2"/>
       <c r="H49" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="21" customHeight="1">
@@ -1859,23 +2366,23 @@
         <v>8</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="G50" s="2"/>
       <c r="H50" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="21" customHeight="1">
@@ -1883,23 +2390,23 @@
         <v>8</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="G51" s="2"/>
       <c r="H51" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1935,42 +2442,42 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15">
       <c r="A1" s="3" t="s">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>116</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="4" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>118</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>119</v>
+        <v>86</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>121</v>
+        <v>88</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>123</v>
+        <v>90</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>124</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1978,7 +2485,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>125</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1986,7 +2493,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/master-db/kgm.xlsx
+++ b/master-db/kgm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kang1\Documents\GitHub\ildeung-battery-v1\master-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9801C83-2B70-4C72-93AE-B2B4B74027A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55943F27-AAE0-4446-8502-54C423D99ADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2132,7 +2132,7 @@
         <v>62</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="G40" s="2"/>
       <c r="H40" s="2" t="s">
